--- a/Final_Merged_Analysis.xlsx
+++ b/Final_Merged_Analysis.xlsx
@@ -2777,7 +2777,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abuzuhri</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>peter-lawrey</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ArneDeutsch</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>spbolton</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>spbolton</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>peter-lawrey</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>peter-lawrey</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>peter-lawrey</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Apurva007</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jdereg</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VerisimilitudeX</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VerisimilitudeX</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VerisimilitudeX</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VerisimilitudeX</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VerisimilitudeX</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VerisimilitudeX</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VerisimilitudeX</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VerisimilitudeX</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VerisimilitudeX</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VerisimilitudeX</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VerisimilitudeX</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ottenhoff</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>peter-lawrey</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>peter-lawrey</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>peter-lawrey</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>peter-lawrey</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>lunasaw</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SimonHalvdansson</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SimonHalvdansson</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SimonHalvdansson</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>shreyashankar</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hansent</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>balthazur</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hansent</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NickHerrig</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PedramNavid</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PedramNavid</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>creatorrr</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michaelvll</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sanchitram1</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mark14wu</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luodian</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>alanlujan91</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ishaan-jaff</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Twixes</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>joamag</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3rdIteration</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3rdIteration</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3rdIteration</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>markrichardson</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dmpetrov</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Torantulino</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Torantulino</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>majdyz</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>achantavy</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>achantavy</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kunaals</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>achantavy</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>areibman</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>areibman</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>adamsachs</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>opcode81</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jlowin</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jxnl</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>scosman</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>leonardmq</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>scosman</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ikamensh</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ikamensh</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ikamensh</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ikamensh</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ikamensh</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ikamensh</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DannyMac180</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DannyMac180</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DannyMac180</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>mgoin</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>dlwh</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>talboren</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>shahargl</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>talboren</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>shahargl</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -14992,7 +14992,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>talboren</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>tssweeney</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>max-sixty</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>rickwierenga</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>rickwierenga</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>mrwadams</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ribalba</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>harupy</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16000,7 +16000,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>jxxghp</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>marius-baseten</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>shaypal5</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>makseq</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>szokeasaurusrex</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16693,7 +16693,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16756,7 +16756,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16945,7 +16945,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17575,7 +17575,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>bmander</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -17792,7 +17792,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>obie</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jonallured</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>obie</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -17981,7 +17981,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>saracarl</t>
+          <t>OpenAI_Codex</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shpigford</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18485,7 +18485,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>delano</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>delano</t>
+          <t>Claude_Code</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -18611,7 +18611,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -18863,7 +18863,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -18989,7 +18989,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>devin-ai-integration[bot]</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
